--- a/excel/TradeMind_Security_500_Report.xlsx
+++ b/excel/TradeMind_Security_500_Report.xlsx
@@ -68,7 +68,7 @@
     <t>Report Timestamp</t>
   </si>
   <si>
-    <t>2026-07-31T05:05:16.960Z</t>
+    <t>2026-07-31T05:17:36.092Z</t>
   </si>
   <si>
     <t>Security Module Name</t>
